--- a/video/quarter.xlsx
+++ b/video/quarter.xlsx
@@ -20,17 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -56,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,17 +440,17 @@
           <t>Riverside Cafe</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
